--- a/tools/importer/reports/import-credit-card-explore.report.xlsx
+++ b/tools/importer/reports/import-credit-card-explore.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="217">
   <si>
     <t>_reportFile</t>
   </si>
@@ -49,15 +49,11 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve">page.evaluate: Error: Failed to import page: para is not defined
-    at eval (eval at evaluate (:290:30), &lt;anonymous&gt;:29:15)
-    at async &lt;anonymous&gt;:316:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">page.evaluate: Error: Failed to import page: para is not defined
-    at eval (eval at evaluate (:290:30), &lt;anonymous&gt;:29:15)
-    at async &lt;anonymous&gt;:316:30
-    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:691:31)
+    <t>page.goto: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:597:20)
     at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
   </si>
   <si>
@@ -67,7 +63,7 @@
     <t>failed</t>
   </si>
   <si>
-    <t>2026-08-28T15:07:25.903Z</t>
+    <t>2026-08-28T16:19:42.238Z</t>
   </si>
   <si>
     <t>https://www.citi.com/credit-cards/?intc=citihpmenu~creditcards~explore</t>
@@ -496,7 +492,7 @@
     <t>credit-card-explore</t>
   </si>
   <si>
-    <t>2026-08-28T15:47:38.326Z</t>
+    <t>2026-08-28T16:56:33.859Z</t>
   </si>
   <si>
     <t>Citi Credit Cards | Apply for a Citi Credit Card | Citi.com</t>
@@ -518,6 +514,138 @@
   </si>
   <si>
     <t>https://www.citi.com/credit-cards/wayfair-credit-cards?category=view-all-credit-cards&amp;intc=citihpmenu~creditcards~explore&amp;afc=161</t>
+  </si>
+  <si>
+    <t>fragments/heroes/brand-citi-strata-credit-cards.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/brand-citi-strata-credit-cards</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:36:36.744Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: brand-citi-strata-credit-cards</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-american-airlines-aadvantage-mileup-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-american-airlines-aadvantage-mileup-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:37:28.626Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-american-airlines-aadvantage-mileup-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-at-and-t-points-plus-card-from-citi.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-at-and-t-points-plus-card-from-citi</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:29:37.532Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-at-and-t-points-plus-card-from-citi</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-aadvantage-business-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-aadvantage-business-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:31:21.342Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-aadvantage-business-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-aadvantage-globe-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-aadvantage-globe-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:19:27.193Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-aadvantage-globe-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-aadvantage-platinum-select-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-aadvantage-platinum-select-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:20:43.679Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-aadvantage-platinum-select-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-diamond-preferred-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-diamond-preferred-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:30:29.607Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-diamond-preferred-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-strata-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-strata-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:32:13.774Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-strata-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-strata-elite-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-strata-elite-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:28:44.580Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-strata-elite-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-strata-premier-card.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-citi-strata-premier-card</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:27:52.637Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-citi-strata-premier-card</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-costco-anywhere-visa-card-by-citi.report.json</t>
+  </si>
+  <si>
+    <t>fragments/heroes/offer-costco-anywhere-visa-card-by-citi</t>
+  </si>
+  <si>
+    <t>2026-08-28T16:18:34.616Z</t>
+  </si>
+  <si>
+    <t>Hero fragment: offer-costco-anywhere-visa-card-by-citi</t>
   </si>
   <si>
     <t>cbol/om/checking/citigold/featured-offer/default.report.json</t>
@@ -924,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1881,16 +2009,368 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
         <v>169</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>170</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>171</v>
       </c>
-      <c r="J30" t="s">
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
         <v>172</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" t="s">
+        <v>174</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>176</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" t="s">
+        <v>178</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>181</v>
+      </c>
+      <c r="I33" t="s">
+        <v>182</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>185</v>
+      </c>
+      <c r="I34" t="s">
+        <v>186</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" t="s">
+        <v>190</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>192</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" t="s">
+        <v>194</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>197</v>
+      </c>
+      <c r="I37" t="s">
+        <v>198</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" t="s">
+        <v>201</v>
+      </c>
+      <c r="I38" t="s">
+        <v>202</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" t="s">
+        <v>205</v>
+      </c>
+      <c r="I39" t="s">
+        <v>206</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>209</v>
+      </c>
+      <c r="I40" t="s">
+        <v>210</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>211</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>213</v>
+      </c>
+      <c r="H41" t="s">
+        <v>214</v>
+      </c>
+      <c r="I41" t="s">
+        <v>215</v>
+      </c>
+      <c r="J41" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-credit-card-explore.report.xlsx
+++ b/tools/importer/reports/import-credit-card-explore.report.xlsx
@@ -492,7 +492,7 @@
     <t>credit-card-explore</t>
   </si>
   <si>
-    <t>2026-08-28T16:56:33.859Z</t>
+    <t>2026-08-28T17:36:48.703Z</t>
   </si>
   <si>
     <t>Citi Credit Cards | Apply for a Citi Credit Card | Citi.com</t>
